--- a/venture/07-automation/tracker/publish-queue/savings-goal-tracker-v1/Savings-Goal-Tracker.xlsx
+++ b/venture/07-automation/tracker/publish-queue/savings-goal-tracker-v1/Savings-Goal-Tracker.xlsx
@@ -630,7 +630,7 @@
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Months from now I'm checking these (enter current month #, e.g. 1):</t>
+          <t>'Months left' = how many months until you want that goal fully funded. Yellow cells are yours to edit.</t>
         </is>
       </c>
     </row>

--- a/venture/07-automation/tracker/publish-queue/savings-goal-tracker-v1/Savings-Goal-Tracker.xlsx
+++ b/venture/07-automation/tracker/publish-queue/savings-goal-tracker-v1/Savings-Goal-Tracker.xlsx
@@ -12,16 +12,20 @@
     <sheet name="52-Week Challenge" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Savings Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="GoalList">'My Goals'!$B$7:$B$14</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00;($#,##0.00)"/>
+    <numFmt numFmtId="167" formatCode="mmm yyyy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -113,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,12 +129,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -205,6 +211,113 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>How close is each goal? (% there)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D6B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'My Goals'!$B$7:$B$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'My Goals'!$F$7:$F$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,9 +607,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E16"/>
+  <dimension ref="B2:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -533,14 +646,14 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1. 'My Goals' tab: name each goal, target amount, target month, and what you've saved so far (yellow cells).</t>
+          <t>1. 'My Goals' tab: name each goal, target amount, months left, and what you've saved so far (yellow cells).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2. The sheet shows exactly how much to save per month to hit each date.</t>
+          <t>2. The sheet shows how much to save per month — and the month each goal is funded ('Funded by').</t>
         </is>
       </c>
     </row>
@@ -554,7 +667,7 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4. 'Savings Log' tab: log each deposit; your goals update as you go.</t>
+          <t>4. 'Savings Log' tab: log each deposit (pick the goal from the dropdown), then update 'Saved so far' on My Goals.</t>
         </is>
       </c>
     </row>
@@ -585,20 +698,46 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>GOOGLE SHEETS USERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Upload this file to Google Drive, then open it — it converts automatically and all formulas work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>The progress chart and dropdowns convert too; chart colors may shift slightly in Sheets. The numbers are identical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Questions? Message us — real humans, fast replies.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -606,9 +745,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G15"/>
+  <dimension ref="B2:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -618,6 +757,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
@@ -630,7 +770,7 @@
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>'Months left' = how many months until you want that goal fully funded. Yellow cells are yours to edit.</t>
+          <t>'Months left' = how many months until you want that goal fully funded. 'Funded by' = the month you'll get there on that plan. Yellow cells are yours to edit.</t>
         </is>
       </c>
     </row>
@@ -665,6 +805,11 @@
           <t>Save per month</t>
         </is>
       </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Funded by (auto)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
@@ -689,6 +834,10 @@
         <f>IF(OR(C7="",E7="",E7=0),"",MAX(0,(C7-D7)/E7))</f>
         <v/>
       </c>
+      <c r="H7" s="10">
+        <f>IF(OR(C7="",E7="",E7=0),"",IF(D7&gt;=C7,"FUNDED!",EDATE(TODAY(),E7)))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
@@ -713,6 +862,10 @@
         <f>IF(OR(C8="",E8="",E8=0),"",MAX(0,(C8-D8)/E8))</f>
         <v/>
       </c>
+      <c r="H8" s="10">
+        <f>IF(OR(C8="",E8="",E8=0),"",IF(D8&gt;=C8,"FUNDED!",EDATE(TODAY(),E8)))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
@@ -737,6 +890,10 @@
         <f>IF(OR(C9="",E9="",E9=0),"",MAX(0,(C9-D9)/E9))</f>
         <v/>
       </c>
+      <c r="H9" s="10">
+        <f>IF(OR(C9="",E9="",E9=0),"",IF(D9&gt;=C9,"FUNDED!",EDATE(TODAY(),E9)))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
@@ -761,9 +918,13 @@
         <f>IF(OR(C10="",E10="",E10=0),"",MAX(0,(C10-D10)/E10))</f>
         <v/>
       </c>
+      <c r="H10" s="10">
+        <f>IF(OR(C10="",E10="",E10=0),"",IF(D10&gt;=C10,"FUNDED!",EDATE(TODAY(),E10)))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr"/>
+      <c r="B11" s="6" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="6" t="n"/>
@@ -775,9 +936,13 @@
         <f>IF(OR(C11="",E11="",E11=0),"",MAX(0,(C11-D11)/E11))</f>
         <v/>
       </c>
+      <c r="H11" s="10">
+        <f>IF(OR(C11="",E11="",E11=0),"",IF(D11&gt;=C11,"FUNDED!",EDATE(TODAY(),E11)))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="6" t="n"/>
@@ -789,9 +954,13 @@
         <f>IF(OR(C12="",E12="",E12=0),"",MAX(0,(C12-D12)/E12))</f>
         <v/>
       </c>
+      <c r="H12" s="10">
+        <f>IF(OR(C12="",E12="",E12=0),"",IF(D12&gt;=C12,"FUNDED!",EDATE(TODAY(),E12)))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="6" t="n"/>
@@ -803,9 +972,13 @@
         <f>IF(OR(C13="",E13="",E13=0),"",MAX(0,(C13-D13)/E13))</f>
         <v/>
       </c>
+      <c r="H13" s="10">
+        <f>IF(OR(C13="",E13="",E13=0),"",IF(D13&gt;=C13,"FUNDED!",EDATE(TODAY(),E13)))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="n"/>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="6" t="n"/>
@@ -817,6 +990,10 @@
         <f>IF(OR(C14="",E14="",E14=0),"",MAX(0,(C14-D14)/E14))</f>
         <v/>
       </c>
+      <c r="H14" s="10">
+        <f>IF(OR(C14="",E14="",E14=0),"",IF(D14&gt;=C14,"FUNDED!",EDATE(TODAY(),E14)))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
@@ -824,26 +1001,38 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="11">
         <f>SUM(C7:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="11">
         <f>SUM(D7:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="10">
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="11">
         <f>SUMIF(G7:G14,"&gt;0")</f>
         <v/>
       </c>
+      <c r="H15" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B2:H2"/>
   </mergeCells>
+  <conditionalFormatting sqref="F7:F14">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="002E7D6B"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -851,7 +1040,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -893,688 +1082,688 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="14">
         <f>SUM(C5:C5)</f>
         <v/>
       </c>
       <c r="E5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="14">
         <f>SUM(C5:C6)</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="14">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
       <c r="E7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="14">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
       <c r="E8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="14">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
       <c r="E9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="14">
         <f>SUM(C5:C10)</f>
         <v/>
       </c>
       <c r="E10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="14">
         <f>SUM(C5:C11)</f>
         <v/>
       </c>
       <c r="E11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="14">
         <f>SUM(C5:C12)</f>
         <v/>
       </c>
       <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="14">
         <f>SUM(C5:C13)</f>
         <v/>
       </c>
       <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="14">
         <f>SUM(C5:C14)</f>
         <v/>
       </c>
       <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="14">
         <f>SUM(C5:C15)</f>
         <v/>
       </c>
       <c r="E15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="14">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
       <c r="E16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="14">
         <f>SUM(C5:C17)</f>
         <v/>
       </c>
       <c r="E17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="14">
         <f>SUM(C5:C18)</f>
         <v/>
       </c>
       <c r="E18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="14">
         <f>SUM(C5:C19)</f>
         <v/>
       </c>
       <c r="E19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="14">
         <f>SUM(C5:C20)</f>
         <v/>
       </c>
       <c r="E20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="14">
         <f>SUM(C5:C21)</f>
         <v/>
       </c>
       <c r="E21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="14">
         <f>SUM(C5:C22)</f>
         <v/>
       </c>
       <c r="E22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="14">
         <f>SUM(C5:C23)</f>
         <v/>
       </c>
       <c r="E23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="14">
         <f>SUM(C5:C24)</f>
         <v/>
       </c>
       <c r="E24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="14">
         <f>SUM(C5:C25)</f>
         <v/>
       </c>
       <c r="E25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="14">
         <f>SUM(C5:C26)</f>
         <v/>
       </c>
       <c r="E26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="14">
         <f>SUM(C5:C27)</f>
         <v/>
       </c>
       <c r="E27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="14">
         <f>SUM(C5:C28)</f>
         <v/>
       </c>
       <c r="E28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="14">
         <f>SUM(C5:C29)</f>
         <v/>
       </c>
       <c r="E29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="14">
         <f>SUM(C5:C30)</f>
         <v/>
       </c>
       <c r="E30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="14">
         <f>SUM(C5:C31)</f>
         <v/>
       </c>
       <c r="E31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="14">
         <f>SUM(C5:C32)</f>
         <v/>
       </c>
       <c r="E32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="14">
         <f>SUM(C5:C33)</f>
         <v/>
       </c>
       <c r="E33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="14">
         <f>SUM(C5:C34)</f>
         <v/>
       </c>
       <c r="E34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="14">
         <f>SUM(C5:C35)</f>
         <v/>
       </c>
       <c r="E35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="14">
         <f>SUM(C5:C36)</f>
         <v/>
       </c>
       <c r="E36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="14">
         <f>SUM(C5:C37)</f>
         <v/>
       </c>
       <c r="E37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="14">
         <f>SUM(C5:C38)</f>
         <v/>
       </c>
       <c r="E38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="14">
         <f>SUM(C5:C39)</f>
         <v/>
       </c>
       <c r="E39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="14">
         <f>SUM(C5:C40)</f>
         <v/>
       </c>
       <c r="E40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="14">
         <f>SUM(C5:C41)</f>
         <v/>
       </c>
       <c r="E41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="14">
         <f>SUM(C5:C42)</f>
         <v/>
       </c>
       <c r="E42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="13" t="n">
         <v>39</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="14">
         <f>SUM(C5:C43)</f>
         <v/>
       </c>
       <c r="E43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="14">
         <f>SUM(C5:C44)</f>
         <v/>
       </c>
       <c r="E44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="14">
         <f>SUM(C5:C45)</f>
         <v/>
       </c>
       <c r="E45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="14">
         <f>SUM(C5:C46)</f>
         <v/>
       </c>
       <c r="E46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="14">
         <f>SUM(C5:C47)</f>
         <v/>
       </c>
       <c r="E47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="14">
         <f>SUM(C5:C48)</f>
         <v/>
       </c>
       <c r="E48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="14">
         <f>SUM(C5:C49)</f>
         <v/>
       </c>
       <c r="E49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="14">
         <f>SUM(C5:C50)</f>
         <v/>
       </c>
       <c r="E50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="13" t="n">
         <v>47</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="14">
         <f>SUM(C5:C51)</f>
         <v/>
       </c>
       <c r="E51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="C52" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="14">
         <f>SUM(C5:C52)</f>
         <v/>
       </c>
       <c r="E52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" s="14" t="n">
         <v>49</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="14">
         <f>SUM(C5:C53)</f>
         <v/>
       </c>
       <c r="E53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="12" t="n">
+      <c r="B54" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="C54" s="9" t="n">
+      <c r="C54" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="14">
         <f>SUM(C5:C54)</f>
         <v/>
       </c>
       <c r="E54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" s="14" t="n">
         <v>51</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="14">
         <f>SUM(C5:C55)</f>
         <v/>
       </c>
       <c r="E55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="14">
         <f>SUM(C5:C56)</f>
         <v/>
       </c>
       <c r="E56" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>Weeks done:</t>
         </is>
       </c>
-      <c r="C58" s="13">
+      <c r="C58" s="15">
         <f>COUNTIF(E5:E56,"&lt;&gt;"&amp;"")</f>
         <v/>
       </c>
@@ -1590,7 +1779,13 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Done marker" error="Pick x from the dropdown (or leave blank)." promptTitle="Done?" prompt="Pick x when the deposit is done." type="list">
+      <formula1>"x"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1598,7 +1793,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1894,12 +2089,12 @@
       <c r="E44" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Total logged</t>
         </is>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="16">
         <f>SUM(D5:D44)</f>
         <v/>
       </c>
@@ -1908,6 +2103,12 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick a goal" error="Pick a goal from the dropdown — it keeps names matching the My Goals tab." promptTitle="Goal" prompt="Pick the goal this deposit belongs to." type="list">
+      <formula1>=GoalList</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>